--- a/survey_templates/035_device_framework_knowledge_quiz--survey_templates.xlsx
+++ b/survey_templates/035_device_framework_knowledge_quiz--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,20 +515,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>first_question</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>first_page</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is your experience level with the device framework?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please choose one of the options.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -538,23 +542,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>first_question</t>
+          <t>years_of_experience</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>first_question</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>How many years do you have working with the device framework?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>This will not affect your score.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,156 +574,184 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>first_question_options</t>
+          <t>device_type</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>first_question_options</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>What type of device do you primarily work with?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please choose all that apply.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>first_answer</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>first_answer</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>What is your role within the team?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Describe your role in the team.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>first_note</t>
+          <t>experience_debugging</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>first_note</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Can you describe your experience with debugging the device framework?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please share any relevant details.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>first_date</t>
+          <t>common_issues</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>first_date</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>What is the most common issue you face with the device framework?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please choose all that apply.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>first_time</t>
+          <t>learning_preferences</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>first_time</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>What is your preferred way to learn about new frameworks?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please choose all that apply.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>first_email</t>
+          <t>workshop_attendance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>first_email</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Have you attended any workshops or conferences related to the device framework?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>This will not affect your score.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>first_phone</t>
+          <t>meetups_attendance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>first_phone</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>How often do you attend online meetups or webinars about the device framework?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>This will not affect your score.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,41 +763,49 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>first_text</t>
+          <t>challenging_project</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>first_text</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Can you describe a challenging project you worked on with the device framework?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please share your story.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>first_integer</t>
+          <t>team_conflicts</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>first_integer</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>How do you handle conflicts with team members when working with the device framework?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>This will not affect your score.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,317 +817,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>first_decimal</t>
+          <t>exciting_feature</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>first_decimal</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>What do you think is the most exciting feature of the device framework?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>This will not affect your score.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>first_date_time</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>first_date_time</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>first_date_time</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>first_date_time</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>first_date_time</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>first_date_time</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>first_text_area</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>first_text_area</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>first_checkbox</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>first_checkbox</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>first_checkbox</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>first_checkbox</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>first_checkbox</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>first_checkbox</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>first_upload</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>first_upload</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>first_upload</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>first_upload</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>first_upload</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>first_upload</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>first_upload</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>first_upload</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>first_dropdown</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>first_dropdown</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>first_dropdown</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>first_dropdown</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +847,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1148,189 +897,189 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>first_question_options_choices</t>
+          <t>device_type_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>device_a</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Device A</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>first_question_options_choices</t>
+          <t>device_type_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>device_b</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Device B</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>first_checkbox_choices</t>
+          <t>device_type_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>device_c</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Device C</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>first_checkbox_choices</t>
+          <t>common_issues_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>bug_a</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Bug A</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>first_checkbox_choices</t>
+          <t>common_issues_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>bug_b</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Bug B</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>first_checkbox_choices</t>
+          <t>common_issues_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>bug_c</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Bug C</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>first_checkbox_choices</t>
+          <t>learning_preferences_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>youtube_tutorials</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>YouTube tutorials</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>first_checkbox_choices</t>
+          <t>learning_preferences_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>online_forums</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Online forums</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>first_dropdown_choices</t>
+          <t>learning_preferences_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>books</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Books</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>first_dropdown_choices</t>
+          <t>learning_preferences_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>instructors</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Instructors</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>first_dropdown_choices</t>
+          <t>workshop_attendance_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1096,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>first_dropdown_choices</t>
+          <t>workshop_attendance_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1358,6 +1107,125 @@
       <c r="C15" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>meetups_attendance_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>meetups_attendance_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>meetups_attendance_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>meetups_attendance_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>team_conflicts_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>confuciusly</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Confuciusly</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>team_conflicts_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>aggressively</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Aggressively</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>team_conflicts_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>cooperatively</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Cooperatively</t>
         </is>
       </c>
     </row>
